--- a/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR TBD.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente Marcelli Emanuele - CR TBD.xlsx
@@ -538,7 +538,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -684,13 +684,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>23</v>
@@ -854,7 +854,7 @@
         <v>27</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>7</v>
@@ -863,14 +863,14 @@
         <v>1</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>25</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>4</v>
@@ -922,7 +922,7 @@
         <v>4</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>0</v>
